--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-20.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-20.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583986845857</v>
+        <v>5583991885432</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Vania</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jose Claudenor Correia Santos</t>
+          <t>Vania do Nascimento Pereira</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583988464476</v>
+        <v>5583986353681</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maciel</t>
+          <t>Girlane</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Maciel Noberto da Silva</t>
+          <t>Girlane Tomaz</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583982322579</v>
+        <v>5583999600558</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Fundacao</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ea Construtora</t>
+          <t>Fundacao Paraibana de Gestao Em Saude -Pb Saude</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583996911204</v>
+        <v>5568984224915</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Manoel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilson Carlos Ferreira dos Santos</t>
+          <t>Manoel de Nazare Ribeiro da Cruz Junior</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583998139483</v>
+        <v>5583988118074</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Idetonio</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jose Edvaldo Cavalcante Costa</t>
+          <t>Idetonio de Franca</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583999616130</v>
+        <v>5583996637543</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carlos Firmo dos Santos</t>
+          <t>Jose Victor Felix Moura</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583987249835</v>
+        <v>5583999122456</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Esvandrro</t>
+          <t>Wallace</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Esvandrro Francisco da Silva</t>
+          <t>Wallace Patrick Santos de Farias Souza</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583998228995</v>
+        <v>5583986397335</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marcelo</t>
+          <t>Danielly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Marcelo Luiz da Nobrega Cunha Santana</t>
+          <t>Danielly de Souza Cruz</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5538999368945</v>
+        <v>5583996332588</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Josias</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Josias Silva do Nascimento</t>
+          <t>Jessica Rodrigues de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583986143808</v>
+        <v>5583987016043</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Otaviano</t>
+          <t>Chislania</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Otaviano Cunha Oliveira</t>
+          <t>Chislania de Lima Felix</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583999329456</v>
+        <v>5583996000868</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gabriela</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gabriela Silva da Costa</t>
+          <t>Fernando Brito da Silva</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583998026480</v>
+        <v>5583988906883</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Climario</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Maria Elisa Celestino da Silva</t>
+          <t>Climario</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583987936825</v>
+        <v>5583982105773</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Geovana</t>
+          <t>Hugo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Geovana Maria Silva Trigo</t>
+          <t>Hugo Fernandes de Castro</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583986807415</v>
+        <v>5583989150934</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Antonio Marcos de Souza Gomes</t>
+          <t>Francisco da Mata</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583988234140</v>
+        <v>5583996546247</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arlindo</t>
+          <t>Joelio</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arlindo Nascimento dos Santos</t>
+          <t>Joelio Santos de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583996310227</v>
+        <v>5583988341679</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rildalene</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rildalene Ribeiro Rolim</t>
+          <t>Francisco Ramalho Sales</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5511986037169</v>
+        <v>5583986845857</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Maria Nasare de Sousa</t>
+          <t>Jose Claudenor Correia Santos</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583996656599</v>
+        <v>5583988464476</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Maciel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Andre Luis Mota Filgueiras</t>
+          <t>Maciel Noberto da Silva</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583988149173</v>
+        <v>5583982322579</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jorge</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jorge Flavio Pereira Martins</t>
+          <t>Ea Construtora</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583996238419</v>
+        <v>5583996911204</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Luiz</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Luiz Renovato da Silva</t>
+          <t>Wilson Carlos Ferreira dos Santos</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583999408331</v>
+        <v>5583998139483</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nivaldo</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nivaldo da Silva Cabral</t>
+          <t>Jose Edvaldo Cavalcante Costa</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5593999529980</v>
+        <v>5583999616130</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Henrique</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Henrique Fonseca Lacerda</t>
+          <t>Carlos Firmo dos Santos</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583987148513</v>
+        <v>5583987249835</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Esvandrro</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jose Geraldo Faustino Gomes</t>
+          <t>Esvandrro Francisco da Silva</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583986444524</v>
+        <v>5583998228995</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ivoneide</t>
+          <t>Marcelo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ivoneide Neves de Carvalho</t>
+          <t>Marcelo Luiz da Nobrega Cunha Santana</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583999364047</v>
+        <v>5538999368945</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Denyallisson</t>
+          <t>Josias</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denyallisson dos Santos Dias</t>
+          <t>Josias Silva do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583987632306</v>
+        <v>5583986143808</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>Otaviano</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Roberto Francisco da Silva</t>
+          <t>Otaviano Cunha Oliveira</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583986185526</v>
+        <v>5583999329456</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Matheus</t>
+          <t>Gabriela</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Matheus Angelo da Costa</t>
+          <t>Gabriela Silva da Costa</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583993458228</v>
+        <v>5583998026480</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>62.192.327</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>62.192.327 Ian Olegario da Trindade Ancores</t>
+          <t>Maria Elisa Celestino da Silva</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583988728667</v>
+        <v>5583987936825</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>Geovana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Paulo da Silva Oliveira</t>
+          <t>Geovana Maria Silva Trigo</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583988866107</v>
+        <v>5583998701254</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Rossana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Maria Selma Morais Barbosa</t>
+          <t>Rossana Marize Almeida Rampcke</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583999116220</v>
+        <v>5583986807415</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Moises</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Moises da Silva Cabral</t>
+          <t>Antonio Marcos de Souza Gomes</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5583981824411</v>
+        <v>5583988234140</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Farmasouza</t>
+          <t>Arlindo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Farmasouza</t>
+          <t>Arlindo Nascimento dos Santos</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583987004512</v>
+        <v>5583996310227</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Edson</t>
+          <t>Rildalene</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Edson do Livramento Martins</t>
+          <t>Rildalene Ribeiro Rolim</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583993628733</v>
+        <v>5511986037169</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wellington Faustino Soares</t>
+          <t>Maria Nasare de Sousa</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583994440110</v>
+        <v>5583996656599</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mundo das Tintas</t>
+          <t>Andre Luis Mota Filgueiras</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583987601356</v>
+        <v>5583998646954</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Simone</t>
+          <t>Felipe</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Simone Lima de Almeida</t>
+          <t>Felipe Benicio da Silva</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583986331990</v>
+        <v>5583988149173</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lucas Alves de Souza Brito</t>
+          <t>Jorge Flavio Pereira Martins</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583993926033</v>
+        <v>5583996238419</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ismael</t>
+          <t>Luiz</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ismael Gomes da Silva</t>
+          <t>Luiz Renovato da Silva</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583988820496</v>
+        <v>5583999408331</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Nivaldo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Antonio Luna Lisboa Neto</t>
+          <t>Nivaldo da Silva Cabral</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583994024580</v>
+        <v>5593999529980</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fabiano</t>
+          <t>Henrique</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fabiano Santiago</t>
+          <t>Henrique Fonseca Lacerda</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5581999040593</v>
+        <v>5583987148513</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Romeu</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Romeu Soares Batista Filho</t>
+          <t>Jose Geraldo Faustino Gomes</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583981960258</v>
+        <v>5583986444524</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Artenuza</t>
+          <t>Ivoneide</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Artenuza Alves</t>
+          <t>Ivoneide Neves de Carvalho</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583998302851</v>
+        <v>5583999364047</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Denyallisson</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Maria do Ceu Sobrinho</t>
+          <t>Denyallisson dos Santos Dias</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583988051376</v>
+        <v>5583987632306</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Luis Carlos da Silva Filho</t>
+          <t>Roberto Francisco da Silva</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583986515736</v>
+        <v>5583986185526</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Luiz</t>
+          <t>Matheus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Luiz Soares da Costa</t>
+          <t>Matheus Angelo da Costa</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5531986981246</v>
+        <v>5583993458228</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Luciana</t>
+          <t>62.192.327</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Luciana Pires</t>
+          <t>62.192.327 Ian Olegario da Trindade Ancores</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583988418324</v>
+        <v>5583988728667</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Laurenice</t>
+          <t>Paulo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Laurenice Victor Souto</t>
+          <t>Paulo da Silva Oliveira</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583998205203</v>
+        <v>5583988866107</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Agencia</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Agencia Sus</t>
+          <t>Maria Selma Morais Barbosa</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583996134625</v>
+        <v>5583999116220</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Moises</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alexandre Lopes da Silva</t>
+          <t>Moises da Silva Cabral</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583998034594</v>
+        <v>5583981824411</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nayanne</t>
+          <t>Farmasouza</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nayanne Gouveia Pinto Lins</t>
+          <t>Farmasouza</t>
         </is>
       </c>
     </row>
